--- a/research/traditional_assets/database/data/bahrain/bahrain_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_brokerage_investment_banking.xlsx
@@ -587,8 +587,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.338</v>
+      <c r="E2">
+        <v>-0.214</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,85 +603,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>82.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="L2">
-        <v>0.2687785760940562</v>
+        <v>0.2375428420775112</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="N2">
-        <v>0.01701693184718795</v>
+        <v>0.1109441812088293</v>
       </c>
       <c r="O2">
-        <v>0.2430133657351154</v>
+        <v>1.065482796892342</v>
       </c>
       <c r="P2">
-        <v>20</v>
+        <v>44.7</v>
       </c>
       <c r="Q2">
-        <v>0.01701693184718795</v>
+        <v>0.05165838437536115</v>
       </c>
       <c r="R2">
-        <v>0.2430133657351154</v>
+        <v>0.4961154273029967</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>51.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.5343749999999999</v>
       </c>
       <c r="U2">
-        <v>525.8</v>
+        <v>619.7</v>
       </c>
       <c r="V2">
-        <v>0.4473751382625712</v>
+        <v>0.7161678030740785</v>
       </c>
       <c r="W2">
-        <v>0.09397122630737612</v>
+        <v>0.09317476732161323</v>
       </c>
       <c r="X2">
-        <v>0.2133667863523325</v>
+        <v>0.6057975914733564</v>
       </c>
       <c r="Y2">
-        <v>-0.1193955600449564</v>
+        <v>-0.5126228241517432</v>
       </c>
       <c r="Z2">
-        <v>0.08383987733420951</v>
+        <v>0.08069354324008085</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1308529801669698</v>
+        <v>0.2141506543139445</v>
       </c>
       <c r="AC2">
-        <v>-0.1308529801669698</v>
+        <v>-0.2141506543139445</v>
       </c>
       <c r="AD2">
-        <v>4259.3</v>
+        <v>6111.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4259.3</v>
+        <v>6111.8</v>
       </c>
       <c r="AG2">
-        <v>3733.5</v>
+        <v>5492.1</v>
       </c>
       <c r="AH2">
-        <v>0.7837375335811283</v>
+        <v>0.8759799916870906</v>
       </c>
       <c r="AI2">
-        <v>0.7791069893358211</v>
+        <v>0.8568704698080671</v>
       </c>
       <c r="AJ2">
-        <v>0.7605728487614081</v>
+        <v>0.8638908987951049</v>
       </c>
       <c r="AK2">
-        <v>0.755600979538969</v>
+        <v>0.8432519576232151</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -706,8 +706,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.338</v>
+      <c r="E3">
+        <v>-0.214</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,85 +722,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>82.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="L3">
-        <v>0.2687785760940562</v>
+        <v>0.2375428420775112</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="N3">
-        <v>0.01701693184718795</v>
+        <v>0.1109441812088293</v>
       </c>
       <c r="O3">
-        <v>0.2430133657351154</v>
+        <v>1.065482796892342</v>
       </c>
       <c r="P3">
-        <v>20</v>
+        <v>44.7</v>
       </c>
       <c r="Q3">
-        <v>0.01701693184718795</v>
+        <v>0.05165838437536115</v>
       </c>
       <c r="R3">
-        <v>0.2430133657351154</v>
+        <v>0.4961154273029967</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>51.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.5343749999999999</v>
       </c>
       <c r="U3">
-        <v>525.8</v>
+        <v>619.7</v>
       </c>
       <c r="V3">
-        <v>0.4473751382625712</v>
+        <v>0.7161678030740785</v>
       </c>
       <c r="W3">
-        <v>0.09397122630737612</v>
+        <v>0.09317476732161323</v>
       </c>
       <c r="X3">
-        <v>0.2133667863523325</v>
+        <v>0.6057975914733564</v>
       </c>
       <c r="Y3">
-        <v>-0.1193955600449564</v>
+        <v>-0.5126228241517432</v>
       </c>
       <c r="Z3">
-        <v>0.08383987733420951</v>
+        <v>0.08069354324008085</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1308529801669698</v>
+        <v>0.2141506543139445</v>
       </c>
       <c r="AC3">
-        <v>-0.1308529801669698</v>
+        <v>-0.2141506543139445</v>
       </c>
       <c r="AD3">
-        <v>4259.3</v>
+        <v>6111.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4259.3</v>
+        <v>6111.8</v>
       </c>
       <c r="AG3">
-        <v>3733.5</v>
+        <v>5492.1</v>
       </c>
       <c r="AH3">
-        <v>0.7837375335811283</v>
+        <v>0.8759799916870906</v>
       </c>
       <c r="AI3">
-        <v>0.7791069893358211</v>
+        <v>0.8568704698080671</v>
       </c>
       <c r="AJ3">
-        <v>0.7605728487614081</v>
+        <v>0.8638908987951049</v>
       </c>
       <c r="AK3">
-        <v>0.755600979538969</v>
+        <v>0.8432519576232151</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/bahrain/bahrain_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_brokerage_investment_banking.xlsx
@@ -587,8 +587,11 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.244</v>
+      </c>
       <c r="E2">
-        <v>-0.214</v>
+        <v>-0.0308</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>90.09999999999999</v>
+        <v>102.9</v>
       </c>
       <c r="L2">
-        <v>0.2375428420775112</v>
+        <v>0.1775056063481111</v>
       </c>
       <c r="M2">
-        <v>96</v>
+        <v>63.01000000000001</v>
       </c>
       <c r="N2">
-        <v>0.1109441812088293</v>
+        <v>0.07354966732811953</v>
       </c>
       <c r="O2">
-        <v>1.065482796892342</v>
+        <v>0.6123420796890184</v>
       </c>
       <c r="P2">
-        <v>44.7</v>
+        <v>58.6</v>
       </c>
       <c r="Q2">
-        <v>0.05165838437536115</v>
+        <v>0.06840200770398039</v>
       </c>
       <c r="R2">
-        <v>0.4961154273029967</v>
+        <v>0.5694849368318756</v>
       </c>
       <c r="S2">
-        <v>51.3</v>
+        <v>4.410000000000004</v>
       </c>
       <c r="T2">
-        <v>0.5343749999999999</v>
+        <v>0.06998889065227747</v>
       </c>
       <c r="U2">
-        <v>619.7</v>
+        <v>1109</v>
       </c>
       <c r="V2">
-        <v>0.7161678030740785</v>
+        <v>1.294502159449049</v>
       </c>
       <c r="W2">
-        <v>0.09317476732161323</v>
+        <v>0.1077035796525016</v>
       </c>
       <c r="X2">
-        <v>0.6057975914733564</v>
+        <v>0.4021588595681728</v>
       </c>
       <c r="Y2">
-        <v>-0.5126228241517432</v>
+        <v>-0.2944552799156712</v>
       </c>
       <c r="Z2">
-        <v>0.08069354324008085</v>
+        <v>0.08991081814656844</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.2141506543139445</v>
+        <v>0.1708021508960377</v>
       </c>
       <c r="AC2">
-        <v>-0.2141506543139445</v>
+        <v>-0.1708021508960377</v>
       </c>
       <c r="AD2">
-        <v>6111.8</v>
+        <v>5502.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6111.8</v>
+        <v>5502.4</v>
       </c>
       <c r="AG2">
-        <v>5492.1</v>
+        <v>4393.4</v>
       </c>
       <c r="AH2">
-        <v>0.8759799916870906</v>
+        <v>0.8652796779418471</v>
       </c>
       <c r="AI2">
-        <v>0.8568704698080671</v>
+        <v>0.8361547579248093</v>
       </c>
       <c r="AJ2">
-        <v>0.8638908987951049</v>
+        <v>0.8368221557684615</v>
       </c>
       <c r="AK2">
-        <v>0.8432519576232151</v>
+        <v>0.8029461217925287</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -706,8 +709,11 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.244</v>
+      </c>
       <c r="E3">
-        <v>-0.214</v>
+        <v>-0.0308</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>90.09999999999999</v>
+        <v>102.9</v>
       </c>
       <c r="L3">
-        <v>0.2375428420775112</v>
+        <v>0.1775056063481111</v>
       </c>
       <c r="M3">
-        <v>96</v>
+        <v>63.01000000000001</v>
       </c>
       <c r="N3">
-        <v>0.1109441812088293</v>
+        <v>0.07354966732811953</v>
       </c>
       <c r="O3">
-        <v>1.065482796892342</v>
+        <v>0.6123420796890184</v>
       </c>
       <c r="P3">
-        <v>44.7</v>
+        <v>58.6</v>
       </c>
       <c r="Q3">
-        <v>0.05165838437536115</v>
+        <v>0.06840200770398039</v>
       </c>
       <c r="R3">
-        <v>0.4961154273029967</v>
+        <v>0.5694849368318756</v>
       </c>
       <c r="S3">
-        <v>51.3</v>
+        <v>4.410000000000004</v>
       </c>
       <c r="T3">
-        <v>0.5343749999999999</v>
+        <v>0.06998889065227747</v>
       </c>
       <c r="U3">
-        <v>619.7</v>
+        <v>1109</v>
       </c>
       <c r="V3">
-        <v>0.7161678030740785</v>
+        <v>1.294502159449049</v>
       </c>
       <c r="W3">
-        <v>0.09317476732161323</v>
+        <v>0.1077035796525016</v>
       </c>
       <c r="X3">
-        <v>0.6057975914733564</v>
+        <v>0.4021588595681728</v>
       </c>
       <c r="Y3">
-        <v>-0.5126228241517432</v>
+        <v>-0.2944552799156712</v>
       </c>
       <c r="Z3">
-        <v>0.08069354324008085</v>
+        <v>0.08991081814656844</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.2141506543139445</v>
+        <v>0.1708021508960377</v>
       </c>
       <c r="AC3">
-        <v>-0.2141506543139445</v>
+        <v>-0.1708021508960377</v>
       </c>
       <c r="AD3">
-        <v>6111.8</v>
+        <v>5502.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6111.8</v>
+        <v>5502.4</v>
       </c>
       <c r="AG3">
-        <v>5492.1</v>
+        <v>4393.4</v>
       </c>
       <c r="AH3">
-        <v>0.8759799916870906</v>
+        <v>0.8652796779418471</v>
       </c>
       <c r="AI3">
-        <v>0.8568704698080671</v>
+        <v>0.8361547579248093</v>
       </c>
       <c r="AJ3">
-        <v>0.8638908987951049</v>
+        <v>0.8368221557684615</v>
       </c>
       <c r="AK3">
-        <v>0.8432519576232151</v>
+        <v>0.8029461217925287</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/bahrain/bahrain_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.244</v>
+        <v>0.3</v>
       </c>
       <c r="E2">
-        <v>-0.0308</v>
+        <v>0.0828</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>102.9</v>
+        <v>111.9</v>
       </c>
       <c r="L2">
-        <v>0.1775056063481111</v>
+        <v>0.1654835847382431</v>
       </c>
       <c r="M2">
-        <v>63.01000000000001</v>
+        <v>61.13</v>
       </c>
       <c r="N2">
-        <v>0.07354966732811953</v>
+        <v>0.05280753282653766</v>
       </c>
       <c r="O2">
-        <v>0.6123420796890184</v>
+        <v>0.5462913315460232</v>
       </c>
       <c r="P2">
-        <v>58.6</v>
+        <v>58.9</v>
       </c>
       <c r="Q2">
-        <v>0.06840200770398039</v>
+        <v>0.05088113337940567</v>
       </c>
       <c r="R2">
-        <v>0.5694849368318756</v>
+        <v>0.5263628239499553</v>
       </c>
       <c r="S2">
-        <v>4.410000000000004</v>
+        <v>2.229999999999997</v>
       </c>
       <c r="T2">
-        <v>0.06998889065227747</v>
+        <v>0.03647963356780626</v>
       </c>
       <c r="U2">
-        <v>1109</v>
+        <v>1081.4</v>
       </c>
       <c r="V2">
-        <v>1.294502159449049</v>
+        <v>0.934174153420871</v>
       </c>
       <c r="W2">
-        <v>0.1077035796525016</v>
+        <v>0.1125528062764031</v>
       </c>
       <c r="X2">
-        <v>0.4021588595681728</v>
+        <v>0.3068648699891871</v>
       </c>
       <c r="Y2">
-        <v>-0.2944552799156712</v>
+        <v>-0.1943120637127839</v>
       </c>
       <c r="Z2">
-        <v>0.08991081814656844</v>
+        <v>0.1255104313609028</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1708021508960377</v>
+        <v>0.1725880255472252</v>
       </c>
       <c r="AC2">
-        <v>-0.1708021508960377</v>
+        <v>-0.1725880255472252</v>
       </c>
       <c r="AD2">
-        <v>5502.4</v>
+        <v>5529.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5502.4</v>
+        <v>5529.5</v>
       </c>
       <c r="AG2">
-        <v>4393.4</v>
+        <v>4448.1</v>
       </c>
       <c r="AH2">
-        <v>0.8652796779418471</v>
+        <v>0.8268905803711624</v>
       </c>
       <c r="AI2">
-        <v>0.8361547579248093</v>
+        <v>0.8338737162763342</v>
       </c>
       <c r="AJ2">
-        <v>0.8368221557684615</v>
+        <v>0.7934959059528693</v>
       </c>
       <c r="AK2">
-        <v>0.8029461217925287</v>
+        <v>0.8015027839342667</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.244</v>
+        <v>0.3</v>
       </c>
       <c r="E3">
-        <v>-0.0308</v>
+        <v>0.0828</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>102.9</v>
+        <v>111.9</v>
       </c>
       <c r="L3">
-        <v>0.1775056063481111</v>
+        <v>0.1654835847382431</v>
       </c>
       <c r="M3">
-        <v>63.01000000000001</v>
+        <v>61.13</v>
       </c>
       <c r="N3">
-        <v>0.07354966732811953</v>
+        <v>0.05280753282653766</v>
       </c>
       <c r="O3">
-        <v>0.6123420796890184</v>
+        <v>0.5462913315460232</v>
       </c>
       <c r="P3">
-        <v>58.6</v>
+        <v>58.9</v>
       </c>
       <c r="Q3">
-        <v>0.06840200770398039</v>
+        <v>0.05088113337940567</v>
       </c>
       <c r="R3">
-        <v>0.5694849368318756</v>
+        <v>0.5263628239499553</v>
       </c>
       <c r="S3">
-        <v>4.410000000000004</v>
+        <v>2.229999999999997</v>
       </c>
       <c r="T3">
-        <v>0.06998889065227747</v>
+        <v>0.03647963356780626</v>
       </c>
       <c r="U3">
-        <v>1109</v>
+        <v>1081.4</v>
       </c>
       <c r="V3">
-        <v>1.294502159449049</v>
+        <v>0.934174153420871</v>
       </c>
       <c r="W3">
-        <v>0.1077035796525016</v>
+        <v>0.1125528062764031</v>
       </c>
       <c r="X3">
-        <v>0.4021588595681728</v>
+        <v>0.3068648699891871</v>
       </c>
       <c r="Y3">
-        <v>-0.2944552799156712</v>
+        <v>-0.1943120637127839</v>
       </c>
       <c r="Z3">
-        <v>0.08991081814656844</v>
+        <v>0.1255104313609028</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1708021508960377</v>
+        <v>0.1725880255472252</v>
       </c>
       <c r="AC3">
-        <v>-0.1708021508960377</v>
+        <v>-0.1725880255472252</v>
       </c>
       <c r="AD3">
-        <v>5502.4</v>
+        <v>5529.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5502.4</v>
+        <v>5529.5</v>
       </c>
       <c r="AG3">
-        <v>4393.4</v>
+        <v>4448.1</v>
       </c>
       <c r="AH3">
-        <v>0.8652796779418471</v>
+        <v>0.8268905803711624</v>
       </c>
       <c r="AI3">
-        <v>0.8361547579248093</v>
+        <v>0.8338737162763342</v>
       </c>
       <c r="AJ3">
-        <v>0.8368221557684615</v>
+        <v>0.7934959059528693</v>
       </c>
       <c r="AK3">
-        <v>0.8029461217925287</v>
+        <v>0.8015027839342667</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/bahrain/bahrain_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_brokerage_investment_banking.xlsx
@@ -645,10 +645,10 @@
         <v>0.1125528062764031</v>
       </c>
       <c r="X2">
-        <v>0.3068648699891871</v>
+        <v>0.306882312808179</v>
       </c>
       <c r="Y2">
-        <v>-0.1943120637127839</v>
+        <v>-0.1943295065317758</v>
       </c>
       <c r="Z2">
         <v>0.1255104313609028</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1725880255472252</v>
+        <v>0.1725910450634976</v>
       </c>
       <c r="AC2">
-        <v>-0.1725880255472252</v>
+        <v>-0.1725910450634976</v>
       </c>
       <c r="AD2">
         <v>5529.5</v>
@@ -767,10 +767,10 @@
         <v>0.1125528062764031</v>
       </c>
       <c r="X3">
-        <v>0.3068648699891871</v>
+        <v>0.306882312808179</v>
       </c>
       <c r="Y3">
-        <v>-0.1943120637127839</v>
+        <v>-0.1943295065317758</v>
       </c>
       <c r="Z3">
         <v>0.1255104313609028</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1725880255472252</v>
+        <v>0.1725910450634976</v>
       </c>
       <c r="AC3">
-        <v>-0.1725880255472252</v>
+        <v>-0.1725910450634976</v>
       </c>
       <c r="AD3">
         <v>5529.5</v>
